--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8624,0.0770,0.0203,0.0256</t>
-  </si>
-  <si>
-    <t>0.0024,0.0018,0.0012,0.9980</t>
-  </si>
-  <si>
-    <t>0.3406,0.0035,0.0010,0.8130</t>
-  </si>
-  <si>
-    <t>0.0114,0.0048,0.0027,0.9914</t>
-  </si>
-  <si>
-    <t>0.9967,0.0006,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9962,0.0016,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9890,0.0056,0.0009,0.0013</t>
-  </si>
-  <si>
-    <t>0.9921,0.0016,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.9923,0.0017,0.0001,0.0020</t>
-  </si>
-  <si>
-    <t>0.9796,0.0467,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0050,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.7668,0.1499,0.0715,0.0150</t>
-  </si>
-  <si>
-    <t>0.4528,0.0215,0.6694,0.0048</t>
-  </si>
-  <si>
-    <t>0.4892,0.0314,0.5928,0.0010</t>
-  </si>
-  <si>
-    <t>0.1268,0.0836,0.7735,0.0398</t>
-  </si>
-  <si>
-    <t>0.8483,0.0894,0.0511,0.0155</t>
-  </si>
-  <si>
-    <t>0.0065,0.9871,0.0059,0.0005</t>
-  </si>
-  <si>
-    <t>0.0168,0.9772,0.0057,0.0007</t>
-  </si>
-  <si>
-    <t>0.1309,0.8868,0.0167,0.0011</t>
-  </si>
-  <si>
-    <t>0.0109,0.9865,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.9969,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.3747,0.0197,0.7256,0.0029</t>
-  </si>
-  <si>
-    <t>0.7762,0.0121,0.1908,0.0139</t>
-  </si>
-  <si>
-    <t>0.0110,0.0036,0.9692,0.0308</t>
-  </si>
-  <si>
-    <t>0.4593,0.0880,0.5018,0.0623</t>
-  </si>
-  <si>
-    <t>0.1716,0.0052,0.9001,0.0029</t>
-  </si>
-  <si>
-    <t>0.0194,0.0087,0.9610,0.0156</t>
-  </si>
-  <si>
-    <t>0.0031,0.0004,0.9935,0.0026</t>
-  </si>
-  <si>
-    <t>0.8226,0.2118,0.0031,0.0075</t>
-  </si>
-  <si>
-    <t>0.4083,0.4687,0.2806,0.0343</t>
-  </si>
-  <si>
-    <t>0.0013,0.0037,0.9922,0.0085</t>
-  </si>
-  <si>
-    <t>0.0038,0.9717,0.1118,0.0002</t>
-  </si>
-  <si>
-    <t>0.7346,0.1622,0.0877,0.0727</t>
-  </si>
-  <si>
-    <t>0.8489,0.1386,0.0348,0.0030</t>
-  </si>
-  <si>
-    <t>0.3702,0.7320,0.0084,0.0007</t>
-  </si>
-  <si>
-    <t>0.0022,0.9887,0.1036,0.0003</t>
-  </si>
-  <si>
-    <t>0.0417,0.8568,0.1152,0.0213</t>
-  </si>
-  <si>
-    <t>0.0161,0.2285,0.9509,0.0015</t>
-  </si>
-  <si>
-    <t>0.0882,0.0909,0.8753,0.0201</t>
-  </si>
-  <si>
-    <t>0.1765,0.0656,0.7815,0.0508</t>
-  </si>
-  <si>
-    <t>0.0331,0.3017,0.8812,0.0105</t>
-  </si>
-  <si>
-    <t>0.0047,0.9803,0.0537,0.0006</t>
-  </si>
-  <si>
-    <t>0.1190,0.0418,0.8821,0.0093</t>
-  </si>
-  <si>
-    <t>0.0087,0.8470,0.0088,0.8239</t>
-  </si>
-  <si>
-    <t>0.0027,0.9835,0.0165,0.0054</t>
-  </si>
-  <si>
-    <t>0.0038,0.9886,0.0269,0.0002</t>
-  </si>
-  <si>
-    <t>0.0057,0.9791,0.0142,0.0012</t>
-  </si>
-  <si>
-    <t>0.0084,0.3236,0.9616,0.0009</t>
-  </si>
-  <si>
-    <t>0.0146,0.0699,0.9689,0.0006</t>
-  </si>
-  <si>
-    <t>0.0452,0.0043,0.9497,0.0100</t>
-  </si>
-  <si>
-    <t>0.0235,0.0046,0.9677,0.0056</t>
-  </si>
-  <si>
-    <t>0.0088,0.0106,0.9911,0.0003</t>
-  </si>
-  <si>
-    <t>0.0064,0.0317,0.9838,0.0005</t>
-  </si>
-  <si>
-    <t>0.9249,0.0982,0.0086,0.0013</t>
-  </si>
-  <si>
-    <t>0.9744,0.0169,0.0030,0.0025</t>
-  </si>
-  <si>
-    <t>0.9807,0.0018,0.0007,0.0087</t>
-  </si>
-  <si>
-    <t>0.0002,0.0344,0.9960,0.0019</t>
-  </si>
-  <si>
-    <t>0.9749,0.0110,0.0048,0.0045</t>
-  </si>
-  <si>
-    <t>0.9939,0.0024,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9370,0.0805,0.0039,0.0021</t>
-  </si>
-  <si>
-    <t>0.0058,0.6749,0.8844,0.0009</t>
-  </si>
-  <si>
-    <t>0.0125,0.0638,0.9613,0.0070</t>
-  </si>
-  <si>
-    <t>0.0129,0.0161,0.9686,0.0205</t>
-  </si>
-  <si>
-    <t>0.0005,0.9229,0.9562,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.0020,0.9945,0.0007</t>
-  </si>
-  <si>
-    <t>0.0057,0.9820,0.0567,0.0002</t>
-  </si>
-  <si>
-    <t>0.0059,0.9894,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.8527,0.0095,0.1853,0.0037</t>
-  </si>
-  <si>
-    <t>0.8054,0.2267,0.0163,0.0036</t>
-  </si>
-  <si>
-    <t>0.0057,0.0059,0.9926,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.9007,0.8206,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.9761,0.5915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.9569,0.2344,0.0018</t>
-  </si>
-  <si>
-    <t>0.0003,0.8033,0.9875,0.0000</t>
-  </si>
-  <si>
-    <t>0.0268,0.0013,0.0242,0.9591</t>
-  </si>
-  <si>
-    <t>0.0030,0.0034,0.0003,0.9983</t>
-  </si>
-  <si>
-    <t>0.0019,0.0008,0.0007,0.9983</t>
-  </si>
-  <si>
-    <t>0.0097,0.0075,0.0112,0.9873</t>
-  </si>
-  <si>
-    <t>0.0058,0.0018,0.0240,0.9888</t>
-  </si>
-  <si>
-    <t>0.0048,0.0032,0.0041,0.9953</t>
-  </si>
-  <si>
-    <t>0.0033,0.9243,0.7496,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.5544,0.9763,0.0002</t>
-  </si>
-  <si>
-    <t>0.0025,0.9308,0.5692,0.0030</t>
-  </si>
-  <si>
-    <t>0.0077,0.2041,0.9468,0.0022</t>
-  </si>
-  <si>
-    <t>0.0002,0.9867,0.8047,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.7626,0.9208,0.0002</t>
-  </si>
-  <si>
-    <t>0.9890,0.0031,0.0008,0.0032</t>
-  </si>
-  <si>
-    <t>0.9618,0.0613,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.9841,0.0239,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9571,0.0776,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9922,0.0078,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9911,0.0090,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9837,0.0092,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.9762,0.0363,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0005,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9906,0.0041,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.9953,0.0011,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9934,0.0039,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9953,0.0019,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9941,0.0013,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9956,0.0015,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9931,0.0047,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0020,0.0008,0.9959,0.0010</t>
-  </si>
-  <si>
-    <t>0.2393,0.0282,0.8038,0.0042</t>
-  </si>
-  <si>
-    <t>0.8548,0.0095,0.0801,0.0180</t>
-  </si>
-  <si>
-    <t>0.0395,0.0035,0.9637,0.0044</t>
-  </si>
-  <si>
-    <t>0.0492,0.9558,0.0043,0.0006</t>
-  </si>
-  <si>
-    <t>0.0335,0.9655,0.0103,0.0003</t>
-  </si>
-  <si>
-    <t>0.0347,0.9607,0.0014,0.0028</t>
-  </si>
-  <si>
-    <t>0.0573,0.9379,0.0081,0.0025</t>
-  </si>
-  <si>
-    <t>0.0325,0.9600,0.0226,0.0012</t>
-  </si>
-  <si>
-    <t>0.0033,0.9927,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.3551,0.7059,0.0170,0.0018</t>
-  </si>
-  <si>
-    <t>0.4261,0.1321,0.5307,0.0743</t>
-  </si>
-  <si>
-    <t>0.3699,0.0377,0.6659,0.0032</t>
-  </si>
-  <si>
-    <t>0.4248,0.2565,0.3908,0.0238</t>
-  </si>
-  <si>
-    <t>0.4132,0.0476,0.6409,0.0070</t>
-  </si>
-  <si>
-    <t>0.4910,0.0190,0.0210,0.6278</t>
-  </si>
-  <si>
-    <t>0.0061,0.9793,0.0412,0.0015</t>
-  </si>
-  <si>
-    <t>0.0028,0.9726,0.0143,0.0145</t>
-  </si>
-  <si>
-    <t>0.1063,0.8846,0.0256,0.0132</t>
-  </si>
-  <si>
-    <t>0.0001,0.9522,0.9706,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.9911,0.0851,0.0003</t>
-  </si>
-  <si>
-    <t>0.7213,0.3525,0.0158,0.0020</t>
-  </si>
-  <si>
-    <t>0.8308,0.2473,0.0071,0.0021</t>
-  </si>
-  <si>
-    <t>0.9842,0.0093,0.0013,0.0015</t>
-  </si>
-  <si>
-    <t>0.9899,0.0036,0.0009,0.0015</t>
-  </si>
-  <si>
-    <t>0.9930,0.0012,0.0004,0.0021</t>
-  </si>
-  <si>
-    <t>0.9917,0.0014,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9918,0.0021,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.9526,0.0166,0.0245,0.0045</t>
-  </si>
-  <si>
-    <t>0.9855,0.0012,0.0008,0.0052</t>
-  </si>
-  <si>
-    <t>0.9801,0.0051,0.0027,0.0053</t>
-  </si>
-  <si>
-    <t>0.0003,0.8458,0.9669,0.0000</t>
-  </si>
-  <si>
-    <t>0.0074,0.6520,0.8462,0.0008</t>
-  </si>
-  <si>
-    <t>0.0129,0.5251,0.8691,0.0036</t>
-  </si>
-  <si>
-    <t>0.0336,0.1056,0.9422,0.0010</t>
-  </si>
-  <si>
-    <t>0.7255,0.1803,0.0579,0.0718</t>
-  </si>
-  <si>
-    <t>0.6361,0.0776,0.3012,0.0193</t>
-  </si>
-  <si>
-    <t>0.2289,0.0023,0.8301,0.0075</t>
-  </si>
-  <si>
-    <t>0.4431,0.3943,0.2608,0.0101</t>
-  </si>
-  <si>
-    <t>0.0074,0.0053,0.0029,0.9929</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0011,0.9997</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0019,0.0017,0.0012,0.9981</t>
-  </si>
-  <si>
-    <t>0.0008,0.9378,0.8940,0.0002</t>
-  </si>
-  <si>
-    <t>0.9758,0.0055,0.0035,0.0083</t>
-  </si>
-  <si>
-    <t>0.7468,0.3094,0.0183,0.0046</t>
-  </si>
-  <si>
-    <t>0.9666,0.0128,0.0077,0.0050</t>
-  </si>
-  <si>
-    <t>0.9196,0.0947,0.0080,0.0041</t>
-  </si>
-  <si>
-    <t>0.9799,0.0071,0.0010,0.0045</t>
-  </si>
-  <si>
-    <t>0.3937,0.0219,0.0058,0.7002</t>
-  </si>
-  <si>
-    <t>0.9372,0.0206,0.0004,0.0181</t>
-  </si>
-  <si>
-    <t>0.0007,0.1282,0.9887,0.0009</t>
-  </si>
-  <si>
-    <t>0.2258,0.0019,0.0052,0.8901</t>
-  </si>
-  <si>
-    <t>0.9625,0.0058,0.0084,0.0120</t>
-  </si>
-  <si>
-    <t>0.2755,0.6674,0.1453,0.0051</t>
-  </si>
-  <si>
-    <t>0.9179,0.0732,0.0154,0.0026</t>
-  </si>
-  <si>
-    <t>0.9421,0.0286,0.0240,0.0018</t>
-  </si>
-  <si>
-    <t>0.3997,0.4924,0.1666,0.1129</t>
-  </si>
-  <si>
-    <t>0.8096,0.0784,0.1010,0.0042</t>
-  </si>
-  <si>
-    <t>0.8372,0.0668,0.1135,0.0133</t>
-  </si>
-  <si>
-    <t>0.9882,0.0024,0.0006,0.0028</t>
-  </si>
-  <si>
-    <t>0.8597,0.1918,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.9910,0.0022,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9895,0.0006,0.0005,0.0051</t>
-  </si>
-  <si>
-    <t>0.9868,0.0083,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.9511,0.0233,0.0126,0.0102</t>
-  </si>
-  <si>
-    <t>0.9931,0.0020,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9861,0.0025,0.0017,0.0031</t>
-  </si>
-  <si>
-    <t>0.3445,0.7313,0.0068,0.0014</t>
-  </si>
-  <si>
-    <t>0.2356,0.8494,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.4462,0.6599,0.0049,0.0008</t>
-  </si>
-  <si>
-    <t>0.1663,0.8009,0.0771,0.0149</t>
-  </si>
-  <si>
-    <t>0.9628,0.0481,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9598,0.0218,0.0128,0.0040</t>
-  </si>
-  <si>
-    <t>0.9842,0.0137,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9257,0.1075,0.0056,0.0012</t>
-  </si>
-  <si>
-    <t>0.0585,0.1177,0.8755,0.0012</t>
-  </si>
-  <si>
-    <t>0.9068,0.1112,0.0133,0.0010</t>
-  </si>
-  <si>
-    <t>0.0029,0.0016,0.9959,0.0005</t>
-  </si>
-  <si>
-    <t>0.0201,0.1262,0.9538,0.0030</t>
-  </si>
-  <si>
-    <t>0.0441,0.0037,0.9567,0.0053</t>
-  </si>
-  <si>
-    <t>0.0245,0.2734,0.9089,0.0026</t>
-  </si>
-  <si>
-    <t>0.0039,0.0069,0.9906,0.0016</t>
-  </si>
-  <si>
-    <t>0.0110,0.0035,0.9896,0.0006</t>
-  </si>
-  <si>
-    <t>0.0127,0.0039,0.9741,0.0145</t>
-  </si>
-  <si>
-    <t>0.2701,0.0302,0.7805,0.0088</t>
-  </si>
-  <si>
-    <t>0.4480,0.0703,0.5348,0.0043</t>
-  </si>
-  <si>
-    <t>0.1675,0.4067,0.4625,0.0068</t>
-  </si>
-  <si>
-    <t>0.1622,0.7270,0.1352,0.0071</t>
-  </si>
-  <si>
-    <t>0.3940,0.1661,0.5201,0.0702</t>
-  </si>
-  <si>
-    <t>0.5519,0.2477,0.2221,0.0090</t>
-  </si>
-  <si>
-    <t>0.2693,0.0424,0.7747,0.0074</t>
-  </si>
-  <si>
-    <t>0.2992,0.0952,0.6296,0.0388</t>
-  </si>
-  <si>
-    <t>0.1230,0.9017,0.0074,0.0006</t>
-  </si>
-  <si>
-    <t>0.3359,0.7873,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.2265,0.7913,0.0030,0.0027</t>
-  </si>
-  <si>
-    <t>0.9470,0.0761,0.0039,0.0017</t>
-  </si>
-  <si>
-    <t>0.1398,0.8863,0.0040,0.0024</t>
-  </si>
-  <si>
-    <t>0.5154,0.2812,0.0960,0.1808</t>
-  </si>
-  <si>
-    <t>0.7260,0.0241,0.2934,0.0069</t>
-  </si>
-  <si>
-    <t>0.8562,0.0195,0.0811,0.0204</t>
-  </si>
-  <si>
-    <t>0.7577,0.0236,0.2243,0.0028</t>
-  </si>
-  <si>
-    <t>0.6505,0.0677,0.2948,0.0207</t>
-  </si>
-  <si>
-    <t>0.0131,0.0159,0.9684,0.0057</t>
-  </si>
-  <si>
-    <t>0.0914,0.1610,0.7950,0.0228</t>
-  </si>
-  <si>
-    <t>0.0313,0.0853,0.9539,0.0020</t>
-  </si>
-  <si>
-    <t>0.0832,0.1826,0.8484,0.0079</t>
-  </si>
-  <si>
-    <t>0.0133,0.7868,0.6587,0.0039</t>
-  </si>
-  <si>
-    <t>0.9919,0.0039,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9876,0.0132,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9884,0.0112,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9903,0.0046,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9905,0.0038,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9915,0.0060,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9925,0.0026,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9934,0.0013,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.0043,0.0011,0.9916,0.0015</t>
-  </si>
-  <si>
-    <t>0.5610,0.1510,0.3675,0.0114</t>
-  </si>
-  <si>
-    <t>0.8839,0.0166,0.0590,0.0316</t>
-  </si>
-  <si>
-    <t>0.0109,0.0061,0.9806,0.0031</t>
-  </si>
-  <si>
-    <t>0.0007,0.0103,0.9966,0.0005</t>
-  </si>
-  <si>
-    <t>0.1152,0.0528,0.8631,0.0058</t>
-  </si>
-  <si>
-    <t>0.0049,0.0077,0.9940,0.0005</t>
-  </si>
-  <si>
-    <t>0.0853,0.0189,0.9060,0.0080</t>
-  </si>
-  <si>
-    <t>0.0113,0.0072,0.9871,0.0017</t>
-  </si>
-  <si>
-    <t>0.0177,0.0203,0.9552,0.0117</t>
-  </si>
-  <si>
-    <t>0.0591,0.3875,0.7589,0.0055</t>
-  </si>
-  <si>
-    <t>0.5764,0.0736,0.4144,0.0308</t>
-  </si>
-  <si>
-    <t>0.4102,0.0064,0.7368,0.0033</t>
-  </si>
-  <si>
-    <t>0.5636,0.1247,0.1175,0.2625</t>
-  </si>
-  <si>
-    <t>0.9794,0.0277,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9851,0.0188,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0027,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9822,0.0170,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9817,0.0210,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9927,0.0043,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9861,0.0114,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.9189,0.1397,0.0027,0.0011</t>
-  </si>
-  <si>
-    <t>0.1189,0.2401,0.6756,0.0081</t>
-  </si>
-  <si>
-    <t>0.0015,0.1241,0.9876,0.0009</t>
-  </si>
-  <si>
-    <t>0.0244,0.1893,0.8670,0.0583</t>
-  </si>
-  <si>
-    <t>0.2314,0.0428,0.7250,0.0021</t>
-  </si>
-  <si>
-    <t>0.0069,0.0054,0.9829,0.0060</t>
-  </si>
-  <si>
-    <t>0.5956,0.0975,0.2670,0.1157</t>
-  </si>
-  <si>
-    <t>0.3148,0.0200,0.6404,0.0564</t>
-  </si>
-  <si>
-    <t>0.0080,0.0299,0.9569,0.0262</t>
-  </si>
-  <si>
-    <t>0.9238,0.0030,0.0111,0.0411</t>
-  </si>
-  <si>
-    <t>0.1326,0.0113,0.0033,0.9519</t>
-  </si>
-  <si>
-    <t>0.0573,0.0407,0.0031,0.9713</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.0008,0.9988</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.8710,0.0284,0.0190,0.0693</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8641,0.0832,0.0289,0.0154</t>
+  </si>
+  <si>
+    <t>0.0085,0.0134,0.0013,0.9937</t>
+  </si>
+  <si>
+    <t>0.7959,0.0386,0.0143,0.0928</t>
+  </si>
+  <si>
+    <t>0.1681,0.0287,0.0067,0.9123</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9959,0.0017,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9942,0.0028,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9906,0.0019,0.0004,0.0025</t>
+  </si>
+  <si>
+    <t>0.9909,0.0036,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.9647,0.0571,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9914,0.0068,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0021,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.6580,0.2683,0.0749,0.0356</t>
+  </si>
+  <si>
+    <t>0.1075,0.0642,0.8771,0.0023</t>
+  </si>
+  <si>
+    <t>0.2826,0.0090,0.8395,0.0007</t>
+  </si>
+  <si>
+    <t>0.1996,0.0113,0.8499,0.0015</t>
+  </si>
+  <si>
+    <t>0.8087,0.0552,0.1020,0.0321</t>
+  </si>
+  <si>
+    <t>0.0016,0.9944,0.0129,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.5174,0.5807,0.0161,0.0008</t>
+  </si>
+  <si>
+    <t>0.0047,0.9911,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.9926,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.6654,0.0317,0.3123,0.0293</t>
+  </si>
+  <si>
+    <t>0.6376,0.0066,0.4689,0.0027</t>
+  </si>
+  <si>
+    <t>0.0566,0.0042,0.9586,0.0025</t>
+  </si>
+  <si>
+    <t>0.0902,0.0106,0.8907,0.0231</t>
+  </si>
+  <si>
+    <t>0.0458,0.0019,0.9715,0.0009</t>
+  </si>
+  <si>
+    <t>0.0291,0.0008,0.9621,0.0073</t>
+  </si>
+  <si>
+    <t>0.0088,0.0055,0.9790,0.0100</t>
+  </si>
+  <si>
+    <t>0.1119,0.9060,0.0034,0.0029</t>
+  </si>
+  <si>
+    <t>0.6624,0.2947,0.1472,0.0201</t>
+  </si>
+  <si>
+    <t>0.0128,0.0217,0.9776,0.0063</t>
+  </si>
+  <si>
+    <t>0.0017,0.9139,0.6580,0.0002</t>
+  </si>
+  <si>
+    <t>0.8372,0.1288,0.0534,0.0092</t>
+  </si>
+  <si>
+    <t>0.1709,0.0613,0.8296,0.0018</t>
+  </si>
+  <si>
+    <t>0.6360,0.4619,0.0115,0.0009</t>
+  </si>
+  <si>
+    <t>0.0152,0.9343,0.4056,0.0019</t>
+  </si>
+  <si>
+    <t>0.1118,0.4811,0.6426,0.0236</t>
+  </si>
+  <si>
+    <t>0.0592,0.1123,0.8720,0.0344</t>
+  </si>
+  <si>
+    <t>0.1521,0.4303,0.5910,0.0255</t>
+  </si>
+  <si>
+    <t>0.0800,0.0054,0.8784,0.0375</t>
+  </si>
+  <si>
+    <t>0.0422,0.1305,0.9047,0.0009</t>
+  </si>
+  <si>
+    <t>0.0215,0.9477,0.0715,0.0009</t>
+  </si>
+  <si>
+    <t>0.0176,0.0116,0.9803,0.0011</t>
+  </si>
+  <si>
+    <t>0.0926,0.7386,0.1123,0.4822</t>
+  </si>
+  <si>
+    <t>0.0003,0.9953,0.0016,0.0065</t>
+  </si>
+  <si>
+    <t>0.0036,0.9748,0.0875,0.0006</t>
+  </si>
+  <si>
+    <t>0.0040,0.9902,0.0062,0.0003</t>
+  </si>
+  <si>
+    <t>0.0193,0.3522,0.7726,0.0497</t>
+  </si>
+  <si>
+    <t>0.0128,0.1700,0.9554,0.0010</t>
+  </si>
+  <si>
+    <t>0.1187,0.1000,0.8078,0.0183</t>
+  </si>
+  <si>
+    <t>0.1197,0.0023,0.9002,0.0064</t>
+  </si>
+  <si>
+    <t>0.0104,0.0029,0.9866,0.0026</t>
+  </si>
+  <si>
+    <t>0.0064,0.0069,0.9892,0.0020</t>
+  </si>
+  <si>
+    <t>0.9800,0.0168,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9606,0.0149,0.0026,0.0116</t>
+  </si>
+  <si>
+    <t>0.9664,0.0303,0.0024,0.0036</t>
+  </si>
+  <si>
+    <t>0.0033,0.0196,0.9925,0.0023</t>
+  </si>
+  <si>
+    <t>0.9907,0.0037,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9832,0.0059,0.0029,0.0036</t>
+  </si>
+  <si>
+    <t>0.9726,0.0320,0.0031,0.0018</t>
+  </si>
+  <si>
+    <t>0.0139,0.5924,0.8480,0.0080</t>
+  </si>
+  <si>
+    <t>0.0067,0.0218,0.9737,0.0095</t>
+  </si>
+  <si>
+    <t>0.0987,0.1769,0.7863,0.0429</t>
+  </si>
+  <si>
+    <t>0.0003,0.8715,0.9867,0.0000</t>
+  </si>
+  <si>
+    <t>0.0111,0.0179,0.9827,0.0015</t>
+  </si>
+  <si>
+    <t>0.0109,0.9303,0.2307,0.0005</t>
+  </si>
+  <si>
+    <t>0.0174,0.9758,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.2097,0.0084,0.8878,0.0030</t>
+  </si>
+  <si>
+    <t>0.7669,0.2627,0.0587,0.0045</t>
+  </si>
+  <si>
+    <t>0.0504,0.0336,0.9284,0.0069</t>
+  </si>
+  <si>
+    <t>0.0024,0.8051,0.8790,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.9214,0.8171,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.9833,0.2385,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.8881,0.8849,0.0004</t>
+  </si>
+  <si>
+    <t>0.1740,0.0171,0.0544,0.8260</t>
+  </si>
+  <si>
+    <t>0.0013,0.0010,0.0009,0.9987</t>
+  </si>
+  <si>
+    <t>0.0014,0.0089,0.0008,0.9978</t>
+  </si>
+  <si>
+    <t>0.0013,0.0036,0.0048,0.9972</t>
+  </si>
+  <si>
+    <t>0.0013,0.0020,0.0100,0.9960</t>
+  </si>
+  <si>
+    <t>0.0051,0.0018,0.0019,0.9956</t>
+  </si>
+  <si>
+    <t>0.0025,0.9326,0.8301,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9105,0.9619,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.6813,0.9239,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.8095,0.9362,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9885,0.3591,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.7279,0.8980,0.0007</t>
+  </si>
+  <si>
+    <t>0.9882,0.0072,0.0015,0.0014</t>
+  </si>
+  <si>
+    <t>0.9833,0.0224,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9885,0.0089,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9824,0.0106,0.0016,0.0028</t>
+  </si>
+  <si>
+    <t>0.9793,0.0129,0.0018,0.0028</t>
+  </si>
+  <si>
+    <t>0.9953,0.0044,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9722,0.0293,0.0015,0.0015</t>
+  </si>
+  <si>
+    <t>0.9819,0.0151,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.9935,0.0037,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9946,0.0042,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9914,0.0028,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.9949,0.0022,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9898,0.0058,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9918,0.0034,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9972,0.0015,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0066,0.0014,0.9925,0.0012</t>
+  </si>
+  <si>
+    <t>0.7127,0.0266,0.2532,0.0257</t>
+  </si>
+  <si>
+    <t>0.7731,0.0206,0.1208,0.0589</t>
+  </si>
+  <si>
+    <t>0.0688,0.0016,0.9622,0.0014</t>
+  </si>
+  <si>
+    <t>0.0524,0.9299,0.0418,0.0015</t>
+  </si>
+  <si>
+    <t>0.0208,0.9722,0.0149,0.0005</t>
+  </si>
+  <si>
+    <t>0.0439,0.9408,0.0042,0.0037</t>
+  </si>
+  <si>
+    <t>0.0815,0.9047,0.0272,0.0021</t>
+  </si>
+  <si>
+    <t>0.0167,0.9776,0.0072,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.9976,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.5979,0.5350,0.0043,0.0016</t>
+  </si>
+  <si>
+    <t>0.5800,0.2927,0.2191,0.0198</t>
+  </si>
+  <si>
+    <t>0.2199,0.0077,0.8583,0.0054</t>
+  </si>
+  <si>
+    <t>0.4884,0.3015,0.2471,0.0503</t>
+  </si>
+  <si>
+    <t>0.4982,0.0748,0.4986,0.0243</t>
+  </si>
+  <si>
+    <t>0.0135,0.0855,0.0524,0.9617</t>
+  </si>
+  <si>
+    <t>0.0006,0.9948,0.0171,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.9955,0.0029,0.0010</t>
+  </si>
+  <si>
+    <t>0.0681,0.9208,0.0141,0.0082</t>
+  </si>
+  <si>
+    <t>0.0006,0.9663,0.8503,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9953,0.0141,0.0001</t>
+  </si>
+  <si>
+    <t>0.6860,0.4357,0.0089,0.0009</t>
+  </si>
+  <si>
+    <t>0.5328,0.5384,0.0182,0.0020</t>
+  </si>
+  <si>
+    <t>0.9827,0.0101,0.0051,0.0013</t>
+  </si>
+  <si>
+    <t>0.9883,0.0028,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.9913,0.0016,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9940,0.0008,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9865,0.0014,0.0003,0.0069</t>
+  </si>
+  <si>
+    <t>0.9818,0.0214,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9837,0.0012,0.0004,0.0073</t>
+  </si>
+  <si>
+    <t>0.9966,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.5515,0.9696,0.0001</t>
+  </si>
+  <si>
+    <t>0.0112,0.4806,0.9341,0.0006</t>
+  </si>
+  <si>
+    <t>0.0117,0.0600,0.9663,0.0007</t>
+  </si>
+  <si>
+    <t>0.0421,0.0756,0.9220,0.0008</t>
+  </si>
+  <si>
+    <t>0.7624,0.0592,0.0247,0.1212</t>
+  </si>
+  <si>
+    <t>0.7321,0.1012,0.2041,0.0070</t>
+  </si>
+  <si>
+    <t>0.0136,0.0017,0.9821,0.0053</t>
+  </si>
+  <si>
+    <t>0.2345,0.4611,0.0351,0.2325</t>
+  </si>
+  <si>
+    <t>0.0598,0.0022,0.0039,0.9712</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0029,0.9992</t>
+  </si>
+  <si>
+    <t>0.0002,0.0122,0.0011,0.9990</t>
+  </si>
+  <si>
+    <t>0.0047,0.0009,0.0014,0.9969</t>
+  </si>
+  <si>
+    <t>0.0015,0.9130,0.8379,0.0007</t>
+  </si>
+  <si>
+    <t>0.9728,0.0113,0.0027,0.0042</t>
+  </si>
+  <si>
+    <t>0.1813,0.8344,0.0053,0.0070</t>
+  </si>
+  <si>
+    <t>0.9348,0.0498,0.0043,0.0082</t>
+  </si>
+  <si>
+    <t>0.3534,0.7525,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9708,0.0038,0.0023,0.0123</t>
+  </si>
+  <si>
+    <t>0.2964,0.0290,0.0026,0.7623</t>
+  </si>
+  <si>
+    <t>0.9808,0.0027,0.0002,0.0059</t>
+  </si>
+  <si>
+    <t>0.0017,0.0768,0.9782,0.0069</t>
+  </si>
+  <si>
+    <t>0.5226,0.0014,0.0158,0.5265</t>
+  </si>
+  <si>
+    <t>0.9258,0.0373,0.0090,0.0134</t>
+  </si>
+  <si>
+    <t>0.4404,0.5855,0.0659,0.0134</t>
+  </si>
+  <si>
+    <t>0.9094,0.0480,0.0316,0.0087</t>
+  </si>
+  <si>
+    <t>0.7928,0.2168,0.0404,0.0055</t>
+  </si>
+  <si>
+    <t>0.2210,0.6538,0.2397,0.0606</t>
+  </si>
+  <si>
+    <t>0.7571,0.2085,0.0762,0.0126</t>
+  </si>
+  <si>
+    <t>0.8416,0.1910,0.0161,0.0017</t>
+  </si>
+  <si>
+    <t>0.9921,0.0038,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9905,0.0052,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9943,0.0027,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9904,0.0003,0.0001,0.0060</t>
+  </si>
+  <si>
+    <t>0.9945,0.0007,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9507,0.0540,0.0028,0.0033</t>
+  </si>
+  <si>
+    <t>0.9948,0.0021,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9909,0.0022,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.5930,0.4005,0.0039,0.0095</t>
+  </si>
+  <si>
+    <t>0.4128,0.7052,0.0051,0.0010</t>
+  </si>
+  <si>
+    <t>0.6755,0.4144,0.0083,0.0012</t>
+  </si>
+  <si>
+    <t>0.2208,0.1891,0.7438,0.0099</t>
+  </si>
+  <si>
+    <t>0.8404,0.0962,0.0101,0.0267</t>
+  </si>
+  <si>
+    <t>0.8874,0.1215,0.0238,0.0095</t>
+  </si>
+  <si>
+    <t>0.9805,0.0131,0.0021,0.0018</t>
+  </si>
+  <si>
+    <t>0.9138,0.0448,0.0411,0.0026</t>
+  </si>
+  <si>
+    <t>0.0085,0.0045,0.9920,0.0009</t>
+  </si>
+  <si>
+    <t>0.9613,0.0303,0.0120,0.0019</t>
+  </si>
+  <si>
+    <t>0.0531,0.0144,0.9557,0.0024</t>
+  </si>
+  <si>
+    <t>0.0152,0.1101,0.9381,0.0159</t>
+  </si>
+  <si>
+    <t>0.0094,0.0026,0.9831,0.0050</t>
+  </si>
+  <si>
+    <t>0.0888,0.4831,0.5143,0.0051</t>
+  </si>
+  <si>
+    <t>0.0442,0.0656,0.9355,0.0014</t>
+  </si>
+  <si>
+    <t>0.0086,0.0007,0.9949,0.0003</t>
+  </si>
+  <si>
+    <t>0.0058,0.0020,0.9896,0.0033</t>
+  </si>
+  <si>
+    <t>0.1780,0.1601,0.7013,0.0241</t>
+  </si>
+  <si>
+    <t>0.1497,0.0332,0.8625,0.0044</t>
+  </si>
+  <si>
+    <t>0.6897,0.0986,0.2176,0.0689</t>
+  </si>
+  <si>
+    <t>0.6192,0.1069,0.3321,0.0135</t>
+  </si>
+  <si>
+    <t>0.1781,0.1717,0.6757,0.0058</t>
+  </si>
+  <si>
+    <t>0.1912,0.5960,0.2069,0.0308</t>
+  </si>
+  <si>
+    <t>0.7636,0.0827,0.1202,0.0405</t>
+  </si>
+  <si>
+    <t>0.5292,0.1144,0.4529,0.0314</t>
+  </si>
+  <si>
+    <t>0.3774,0.7025,0.0079,0.0011</t>
+  </si>
+  <si>
+    <t>0.0444,0.9654,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.8355,0.2218,0.0097,0.0019</t>
+  </si>
+  <si>
+    <t>0.9849,0.0141,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.2254,0.8246,0.0125,0.0028</t>
+  </si>
+  <si>
+    <t>0.4124,0.4659,0.1693,0.0583</t>
+  </si>
+  <si>
+    <t>0.8901,0.0360,0.0625,0.0049</t>
+  </si>
+  <si>
+    <t>0.8500,0.0214,0.0816,0.0239</t>
+  </si>
+  <si>
+    <t>0.8739,0.0157,0.1051,0.0037</t>
+  </si>
+  <si>
+    <t>0.3697,0.0728,0.6175,0.0279</t>
+  </si>
+  <si>
+    <t>0.0169,0.0034,0.9794,0.0048</t>
+  </si>
+  <si>
+    <t>0.1828,0.1628,0.7121,0.0215</t>
+  </si>
+  <si>
+    <t>0.0423,0.0187,0.9570,0.0045</t>
+  </si>
+  <si>
+    <t>0.1324,0.0302,0.8714,0.0091</t>
+  </si>
+  <si>
+    <t>0.0174,0.5971,0.6095,0.0106</t>
+  </si>
+  <si>
+    <t>0.9929,0.0025,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9884,0.0060,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9913,0.0076,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9765,0.0271,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.9819,0.0125,0.0023,0.0015</t>
+  </si>
+  <si>
+    <t>0.9952,0.0036,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9944,0.0019,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9872,0.0163,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0319,0.0078,0.9654,0.0066</t>
+  </si>
+  <si>
+    <t>0.0360,0.9343,0.0529,0.0056</t>
+  </si>
+  <si>
+    <t>0.9297,0.0334,0.0152,0.0096</t>
+  </si>
+  <si>
+    <t>0.0231,0.0162,0.9728,0.0016</t>
+  </si>
+  <si>
+    <t>0.0006,0.0052,0.9978,0.0006</t>
+  </si>
+  <si>
+    <t>0.0801,0.0127,0.9305,0.0031</t>
+  </si>
+  <si>
+    <t>0.0025,0.0090,0.9951,0.0008</t>
+  </si>
+  <si>
+    <t>0.3867,0.0156,0.6985,0.0033</t>
+  </si>
+  <si>
+    <t>0.0036,0.0120,0.9914,0.0019</t>
+  </si>
+  <si>
+    <t>0.0025,0.0054,0.9754,0.0417</t>
+  </si>
+  <si>
+    <t>0.1200,0.1927,0.7702,0.0080</t>
+  </si>
+  <si>
+    <t>0.7212,0.0215,0.2457,0.0251</t>
+  </si>
+  <si>
+    <t>0.6433,0.0074,0.4771,0.0040</t>
+  </si>
+  <si>
+    <t>0.6945,0.0113,0.1120,0.1332</t>
+  </si>
+  <si>
+    <t>0.9870,0.0074,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9701,0.0382,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9959,0.0011,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9685,0.0442,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9943,0.0017,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9858,0.0114,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9933,0.0019,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9920,0.0041,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.4678,0.0138,0.6243,0.0029</t>
+  </si>
+  <si>
+    <t>0.0022,0.0111,0.9896,0.0016</t>
+  </si>
+  <si>
+    <t>0.0366,0.0594,0.9329,0.0024</t>
+  </si>
+  <si>
+    <t>0.1682,0.0195,0.8383,0.0173</t>
+  </si>
+  <si>
+    <t>0.0455,0.0131,0.9484,0.0054</t>
+  </si>
+  <si>
+    <t>0.3269,0.0119,0.5158,0.1313</t>
+  </si>
+  <si>
+    <t>0.3413,0.0356,0.6444,0.0653</t>
+  </si>
+  <si>
+    <t>0.0614,0.2199,0.7105,0.1537</t>
+  </si>
+  <si>
+    <t>0.8550,0.0043,0.0048,0.1639</t>
+  </si>
+  <si>
+    <t>0.0046,0.0634,0.0015,0.9926</t>
+  </si>
+  <si>
+    <t>0.0444,0.0053,0.0022,0.9832</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.0017,0.9989</t>
+  </si>
+  <si>
+    <t>0.0010,0.0050,0.0003,0.9990</t>
+  </si>
+  <si>
+    <t>0.1452,0.0569,0.0292,0.9045</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,10 +3418,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
